--- a/Test_data/New_Architecture/Complex_Scenario/Marks_Good.xlsx
+++ b/Test_data/New_Architecture/Complex_Scenario/Marks_Good.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1040,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1960,7 +1960,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2303,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2381,7 +2381,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2407,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2433,7 +2433,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2993,22 +2993,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3043,22 +3043,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -3068,22 +3068,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3093,22 +3093,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3118,22 +3118,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3168,22 +3168,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -3218,22 +3218,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3268,22 +3268,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3293,22 +3293,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3368,22 +3368,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -3418,22 +3418,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -3443,22 +3443,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -3468,22 +3468,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -3518,22 +3518,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -3618,22 +3618,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -3643,22 +3643,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -3668,22 +3668,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -3693,22 +3693,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
         <v>9</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -3806,7 +3806,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3844,22 +3844,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3869,22 +3869,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3919,22 +3919,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3969,19 +3969,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -3994,22 +3994,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4019,22 +4019,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4044,22 +4044,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -4094,22 +4094,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -4119,22 +4119,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -4144,22 +4144,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -4169,22 +4169,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -4194,22 +4194,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -4244,22 +4244,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4269,22 +4269,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4294,22 +4294,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4319,22 +4319,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4369,22 +4369,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -4394,22 +4394,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4419,22 +4419,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4444,22 +4444,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4469,22 +4469,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4494,22 +4494,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -4519,22 +4519,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Test_data/New_Architecture/Complex_Scenario/Marks_Good.xlsx
+++ b/Test_data/New_Architecture/Complex_Scenario/Marks_Good.xlsx
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -528,7 +528,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
@@ -593,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -710,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>4</v>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>4</v>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -910,7 +910,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -936,7 +936,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -962,7 +962,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -1001,7 +1001,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -1040,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1066,7 +1066,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1157,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>4</v>
@@ -1248,7 +1248,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1552,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1565,7 +1565,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
@@ -1617,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1804,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1869,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1921,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1947,7 +1947,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -1973,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
@@ -2025,7 +2025,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -2160,7 +2160,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -2303,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2368,7 +2368,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2394,7 +2394,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2446,7 +2446,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>4</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2498,7 +2498,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2511,7 +2511,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2555,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2568,7 +2568,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2581,7 +2581,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2607,7 +2607,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2659,7 +2659,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
@@ -2993,22 +2993,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -3021,19 +3021,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3043,22 +3043,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3068,22 +3068,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3096,19 +3096,19 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3121,19 +3121,19 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3171,19 +3171,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3193,19 +3193,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>8</v>
@@ -3221,19 +3221,19 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -3246,19 +3246,19 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3271,16 +3271,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -3296,19 +3296,19 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3368,22 +3368,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -3393,19 +3393,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>8</v>
@@ -3430,10 +3430,10 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -3455,10 +3455,10 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -3468,22 +3468,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -3524,13 +3524,13 @@
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
         <v>7</v>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>8</v>
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -3593,19 +3593,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
         <v>7</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>7</v>
@@ -3630,7 +3630,7 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>9</v>
@@ -3643,22 +3643,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3668,19 +3668,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
@@ -3693,22 +3693,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -3721,19 +3721,19 @@
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -3831,7 +3831,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -3847,7 +3847,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -3875,16 +3875,16 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3897,7 +3897,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -3909,7 +3909,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3919,22 +3919,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3947,19 +3947,19 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3969,13 +3969,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -3984,7 +3984,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -4059,7 +4059,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
@@ -4109,7 +4109,7 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
@@ -4128,13 +4128,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4144,22 +4144,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -4178,10 +4178,10 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
@@ -4203,7 +4203,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -4225,13 +4225,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -4244,16 +4244,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -4294,22 +4294,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4322,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
@@ -4334,7 +4334,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4347,16 +4347,16 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -4378,13 +4378,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4394,22 +4394,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -4419,16 +4419,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -4447,7 +4447,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -4478,13 +4478,13 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4497,13 +4497,13 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -4531,10 +4531,10 @@
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
